--- a/竹光國中115學年度總量管制知識庫.xlsx
+++ b/竹光國中115學年度總量管制知識庫.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
     <col width="58" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
     <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="37.10000000000001" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
     <col width="11.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -484,7 +484,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>觸發關鍵字 (逗號分隔)</t>
+          <t>觸發關鍵字 (逗號分隔；a+b=同時出現；-詞=排除)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -514,29 +514,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>順位判定</t>
+          <t>順位總覽</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>自有,權狀,房屋稅,二順位,自用住宅</t>
+          <t>哪些順位,幾個順位,順位有哪些,所有順位,全部順位,順位總覽,六大順位,六個順位,順位介紹,順位說明,順位怎麼分,順位分幾,順位是什麼,什麼是順位,順位有幾,順位的定義,順位一覽,各順位,-一順位,-二順位,-三順位,-四順位,-五順位,-六順位,-1順位,-2順位,-3順位,-4順位,-5順位,-6順位</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>我們在學區內有自用住宅，小孩是民富國小畢業，算第幾順位？</t>
+          <t>總量管制有哪些順位？六大順位分別是什麼？</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>🎯【判定結果：第二順位】
-依 115 作業規定：設籍並實際居住本校學區內之「新竹市」國小應屆畢業生，且戶籍與直系親屬同戶，檢附自有房屋所有權狀（或當年度房屋稅籍證明）並簽具家訪同意書者，列為【第二順位】！
-※ 若為外縣市國小畢業生則列為第三順位。</t>
+          <t>📚【115學年度竹光國中 錄取順位總覽】
+━━━━━━━━━━━━━━
+先決條件：學生設籍並實際居住學區內，且戶籍內至少有一位直系尊親屬（父母／祖父母／外祖父母）或法定監護人同戶。戶籍不符者連順位都沒有。
+• 第一順位：少年保護個案、列冊低收入戶子女、父母雙亡學童、本校編制內教職員工子女、市府鑑定安置之資源生
+• 第二順位：新竹市國小畢業生＋完整居住證明（自有權狀／115房屋稅籍證明，或法院公證租約）＋家訪同意書
+• 第三順位：外縣市國小畢業生＋完整居住證明＋家訪同意書
+• 第四順位：僅提供「未經法院公證」的租約（租期涵蓋 115/3/14～9/1）＋家訪同意書
+• 第五順位：戶籍符合但無法提供居住證明（或文件不符規定）＋家訪同意書
+• 第六順位（最後順位）：無法簽具家訪同意書，或經查為空戶／非實際居住者
+排序規則：先比順位，同順位再比戶籍遷入學區時間先後。
+想知道自己是第幾順位？直接輸入「我有權狀」「租約沒公證」「沒有租約」等描述即可試算！</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、三、2</t>
+          <t>作業規定伍、一～三；簡報「錄取順位」</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -556,24 +564,29 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>未公證,租約,四順位,沒公證,租屋未公證</t>
+          <t>一順位,第1順位,低收,低收入,教職員,老師的小孩,父母雙亡,安置,資源生,少年保護,特殊身分</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>在學區內租屋但「沒有經過法院公證」，還可以登記嗎？排第幾順位？</t>
+          <t>第一順位是哪些人？教職員子女、低收入戶算第一順位嗎？</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>📋【判定結果：第四順位】
-依 115 作業規定：只要戶籍符合（與直系親屬同戶），即可參加新生登記！若僅提供「未經法院公證之房屋租賃契約」（租期須涵蓋 115/3/14~115/9/1，承租人為直系尊親屬）並簽具家訪同意書者，列為【第四順位】！
-💡 提示：若能補辦法院公證，順位可提升為第二順位！</t>
+          <t>🥇【第一順位：法定特殊身分】
+依 115 作業規定，下列身分且設籍本校學區者列為第一順位：
+1. 經縣市政府轉介安置之少年保護個案
+2. 設籍本市且居住學區內、經市府列冊之低收入戶子女
+3. 設籍本市且居住學區內而父母雙亡者
+4. 本校現職編制內教職員工之子女、受監護人（隨父母或監護人就讀所服務學校；名單公告後新聘者採外加名額）
+5. 經市府鑑定並安置之資源生
+※ 除教職員子女外，學校會實地訪查是否有居住事實。</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、三、4 (115重要規則)</t>
+          <t>作業規定伍、三、1；簡報「錄取順位」第一順位</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -593,23 +606,26 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>公證租約,法院公證,租賃公證,租屋二順位</t>
+          <t>自有,權狀,所有權狀,房屋稅,稅籍,自用住宅,自己的房子,二順位,第2順位,買房</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>租屋若有辦理「法院公證租賃契約」，可以排第幾順位？</t>
+          <t>我們在學區內有自用住宅（有房屋所有權狀），算第幾順位？</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>⚖️【判定結果：第二順位（本市）/ 第三順位（外縣市）】
-租賃房屋若能提供「經法院公證之房屋租賃契約證明」（租賃日期須涵蓋 115/3/14 新生登記日至 115/9/1 開學日，承租人為直系尊親屬），並簽具家訪同意書，新竹市國小畢業生列為【第二順位】、外縣市畢業生列為【第三順位】！</t>
+          <t>🎯【判定結果：第二順位（本市國小）／第三順位（外縣市國小）】
+依 115 作業規定：設籍並實際居住本校學區內、戶籍與直系尊親屬同戶，檢附「登記於直系尊親屬或法定監護人名下」的房屋所有權狀（或 115 年度房屋稅籍證明），並簽具家訪同意書者：
+• 新竹市國小應屆畢業生 ➔【第二順位】
+• 外縣市國小應屆畢業生 ➔【第三順位】
+※ 自有住宅與公證租約在排序上完全相同，都是第二（或第三）順位。</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、三、2 &amp; 3</t>
+          <t>作業規定伍、三、2 &amp; 3；簡報 Q2-2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -629,23 +645,26 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>無證明,五順位,沒有權狀,沒有租約</t>
+          <t>公證,法院公證,租賃公證,公證租約,有公證,已公證,-未公證,-沒公證,-沒有公證,-無公證,-不公證,-沒去公證,-還沒公證,-尚未公證,-未經公證</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>如果戶籍在學區內，但無法提供任何房屋權狀或租約，還能登記嗎？</t>
+          <t>租屋若有辦理「法院公證租賃契約」，可以排第幾順位？</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>📌【判定結果：第五順位】
-只要戶籍符合（設籍學區且有直系親屬同戶），就算無法提供居住證明文件或文件不符規定，只要簽具家訪同意書，仍可列為【第五順位】進行排序錄取！</t>
+          <t>⚖️【判定結果：第二順位（本市）／第三順位（外縣市）】
+租屋家庭若能提供「經法院公證之房屋租賃契約」（租賃期間須涵蓋 115/3/14 新生登記日至 115/9/1 開學日，承租人須為學生的直系尊親屬或法定監護人），並簽具家訪同意書：
+• 新竹市國小畢業生 ➔【第二順位】
+• 外縣市國小畢業生 ➔【第三順位】
+公證租約與自有權狀在排序上效力相同。</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、三、5</t>
+          <t>作業規定伍、三、2 &amp; 3；Q&amp;A Q8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -660,32 +679,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>門檻分析</t>
+          <t>順位判定</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>幾年,幾歲,門檻,排得上嗎,大班,小二,歷史數據</t>
+          <t>未公證,沒公證,沒有公證,無公證,不公證,沒去公證,還沒公證,尚未公證,未經公證,一般租約,普通租約,四順位,第4順位,租約沒有公證,-沒有租約,-沒租約,-無租約,-沒有租賃</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>設籍大約要滿幾年才排得上竹光國中？</t>
+          <t>在學區內租屋但「租約沒有經過法院公證」，還可以登記嗎？排第幾順位？</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>📊【歷年第四順位設籍門檻參考】：
-• 111學年：設籍滿 5 年 (約國小二年級設籍)
-• 112學年：設籍滿 4 年 (約國小三年級設籍)
-• 113學年：設籍滿 8 年 (約幼兒園大班設籍)
-• 114學年：設籍滿 2 年 (約國小五年級設籍)
-每年人數不同，需待 3/14 現場登記排序後方能確定。先比順位，同順位再依設籍先後決定！</t>
+          <t>📋【判定結果：第四順位】
+依 115 作業規定：只要戶籍符合（設籍學區且與直系尊親屬同戶），就可以參加新生登記！
+若僅能提供「未經法院公證的房屋租賃契約」（租期須涵蓋 115/3/14～115/9/1，承租人為直系尊親屬），並簽具家訪同意書，列為【第四順位】。
+💡 提示：若能在 3/14 登記前補辦法院公證，即可提升為第二順位（外縣市國小為第三順位）。</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>新生入學簡報 P.27</t>
+          <t>作業規定伍、三、4；Q&amp;A Q8；簡報「錄取順位(新增)」</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -700,29 +717,31 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>設籍計算</t>
+          <t>順位判定</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>累計,搬家,學區內遷移,遷出,金雅里,重算</t>
+          <t>五順位,第5順位,沒有租約,沒租約,無租約,沒有租賃,沒有簽約,沒簽約,口頭租,沒有租屋證明,沒有居住證明,無居住證明,沒有證明,沒證明,無證明,沒有文件,沒有權狀,無權狀,提不出,拿不出,住親戚家,住爺爺家,住阿公家,住外公家,住娘家,住公司宿舍,居住文件不符</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>之前在學區內搬家設籍時間可以累計嗎？中途遷出新竹市怎麼算？</t>
+          <t>我是租房子但沒有租約（或沒有任何居住證明），算第幾順位？</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>🏡【設籍時間計算關鍵原則】：
-1. 【學區內遷移 ➔ 時間可連續累計】：同一學區內里鄰搬遷（如境福里遷到磐石里），設籍時間得以累計！
-2. 【中途遷出學區 ➔ 重新計算】：若中途曾遷出學區（如遷至金雅里），再遷回竹光學區，則以「最後一次遷入本學區日期為設籍日」！</t>
+          <t>📌【判定結果：第五順位】
+依 115 作業規定：只要戶籍符合（學生設籍學區，且戶籍內有直系尊親屬或法定監護人同戶），即使無法提供任何居住證明文件（沒有權狀、沒有租約），或提供的文件不符規定（例如承租人不是直系尊親屬、租期未涵蓋 3/14～9/1），只要簽具家訪同意書，仍可列為【第五順位】參加排序。
+💡 想提升順位：
+• 補一份「未公證」租約（租期涵蓋 115/3/14～9/1、承租人為直系尊親屬）➔ 第四順位
+• 租約再去法院公證 ➔ 第二順位（外縣市國小為第三順位）</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、二 &amp; Q&amp;A Q3</t>
+          <t>作業規定伍、三、5；簡報 Q7「沒有居住證明文件會列為第四或五順位」</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -737,34 +756,33 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>現場登記</t>
+          <t>順位判定</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>3/14,帶什麼,文件,證件,黃單,戶籍謄本,戶口名簿</t>
+          <t>順位的差別,順位差別,順位有什麼不同,順位差異,順位不同,順位不一樣,差別+順位,差異+順位,不同+順位,四跟五,四和五,四與五,4跟5,4和5,四五順位,第四第五,二跟四,二和四,公證跟未公證,公證與未公證,公證和未公證</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3/14 (六) 新生入學現場登記要帶哪些文件？一定要本人到場嗎？</t>
+          <t>第四順位跟第五順位的差別是什麼？第二、第四、第五怎麼分？</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>🎒【3/14 (六) 現場審核應備文件清單】：
-時間：115年3月14日(六) 上午 08:00 - 11:00
-地點：竹光國中
-應備文件：
-1. 📄 新生入學通知單（黃單，背面登記表及家訪同意書填妥簽名）
-2. 👥 戶籍證明（必要二擇一）：3個月內全戶謄本正本 或 新式戶口名簿正本＋影本（須具詳細記事）
-3. 🏠 居住證明（自有權狀 / 稅籍證明 / 公證租約 / 未公證租約）
-※ 可委託親友到校送件。未參加登記者視同放棄！</t>
+          <t>🔍【第二／第四／第五順位 差別一次看懂】
+三者戶籍條件都一樣（設籍學區＋直系尊親屬同戶＋簽家訪同意書），差別只在「居住證明文件」：
+• 第二順位（外縣市國小為第三）：有「完整」居住證明 ➔ 自有房屋所有權狀／115 房屋稅籍證明，或「經法院公證」的租約
+• 第四順位：只有「未經法院公證」的租約（租期涵蓋 115/3/14～9/1，承租人為直系尊親屬）
+• 第五順位：完全沒有居住證明（沒權狀、沒租約），或文件不符規定
+一句話：有公證租約＝第二、租約沒公證＝第四、連租約都沒有＝第五。
+同一順位內再依戶籍遷入學區時間先後排序。</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>新生入學簡報 P.21 &amp; P.36</t>
+          <t>作業規定伍、三、2～5；Q&amp;A Q8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,29 +797,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>戶籍規定</t>
+          <t>順位判定</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>直系,寄居,戶籍不符,爸爸媽媽,爺爺奶奶</t>
+          <t>六順位,第6順位,最後順位,末順位,家訪同意書,不簽,拒簽,不同意家訪,空戶,人籍分離,沒有住,非實際居住,不是真的住,查核,實地訪查</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>學生戶籍內一定要有直系親屬同戶嗎？寄居親戚家可以嗎？</t>
+          <t>第六順位（最後順位）是什麼情況？不簽家訪同意書會怎樣？</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>⚠️【戶籍必要要件】：
-學生戶籍內「必須至少有一位直系尊親屬或法定監護人」（父、母、祖父、祖母、外公、外婆）同一戶籍！
-若僅有學生一人設籍或寄居非直系親屬家，則【連順位都沒有】，無法參加新生登記！請儘速辦理直系親屬遷入。</t>
+          <t>⚠️【第六順位（最後順位）】
+依 115 作業規定，下列情形列為第六順位（最後順位）錄取：
+1. 符合入學資格，但無法簽具（或不同意）家訪同意書者
+2. 經學校訪查發現已遷居學區外、非實際居住或為「空戶」（人籍分離）者 ➔ 列第六順位並勸導轉入實際居住學區的學校
+※ 家訪同意書在黃單背面，請務必簽名；學校得視需求不定期查核居住事實。
+※ 若戶籍內沒有直系尊親屬同戶，則「無法參加新生登記」，連順位都沒有（這不是第六順位）。</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、一 &amp; 簡報 P.33</t>
+          <t>作業規定伍、三、6 &amp; 伍、五；簡報「最後順位」</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -816,37 +837,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>學區查詢</t>
+          <t>順位判定</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>學區,里鄰,民富,磐石,北門,境福,新雅,客雅,南勢,中雅</t>
+          <t>怎麼排,怎麼排序,排序,先比,誰先,優先順序,先後順序,排序原則,排序規則,錄取標準,錄取原則,怎麼錄取,如何錄取,依據什麼</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>請問竹光國中的學區有哪些里別？北門里算學區嗎？</t>
+          <t>錄取排序原則是什麼？先比什麼？</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>🗺️【竹光國中 115學年度學區劃分】：
-• 單一學區：民富里、磐石里、新雅里 1-18 及 20-27 鄰
-• 共同學區：
-  - 北門里 1-5、7-10、12、13、16、17 鄰 ➔ 竹光、光華、建華 (115新增)
-  - 新雅里 19 鄰 ➔ 竹光、虎林
-  - 南勢里、客雅里 ➔ 竹光、虎林、成德
-  - 境福里 ➔ 竹光、光華
-  - 文雅里 ➔ 竹光、成德、光華
-  - 長和里、新民里 ➔ 竹光、育賢、光華
-  - 中雅里 ➔ 竹光、成德、虎林
-※ 共同學區與單一學區排序標準完全一致。</t>
+          <t>📐【錄取排序原則】
+1. 先比「順位」：第一順位全部排完，才輪到第二順位，依此類推。
+2. 同順位再比「戶籍遷入學區時間」：越早設籍越優先。
+3. 最後一名若有二人以上同日遷入：有兄姊就讀本校者優先；條件相同則公開抽籤。
+4. 最後一名若為多胞胎之一：其多胞胎手足以外加名額隨同就讀。
+5. 超出核定名額者依序列為備取。
+※ 共同學區與單一學區的排序基準完全一樣；自有住宅與公證租約也一樣（皆第二順位）。</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>市府115學區劃分表 &amp; 簡報 P.31</t>
+          <t>作業規定伍、四；Q&amp;A Q2；簡報「錄取標準」</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -861,28 +878,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>共同學區</t>
+          <t>門檻分析</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>兩所登記,光華,雙重登記,3/12,北門里雙登記</t>
+          <t>幾年,幾歲,門檻,排得上,排的上,排得到,排不排得,多久,歷年,往年,去年,大班,小二,小三,小五,設籍多久,設籍幾年,要住多久,錄取線</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>北門里是共同學區，如果想同時登記竹光國中跟光華國中可以嗎？</t>
+          <t>設籍大約要滿幾年才排得上竹光國中？</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>⚖️【共同學區雙總量國中登記手續】：
-可以！但家長務必於【115年3月12日(四)前】，自行向另一所總量限制國中（如光華國中）提出登記申請手續！逾期將無法同時登記兩校。</t>
+          <t>📊【歷年第四順位設籍門檻參考】
+• 111學年：設籍滿 5 年（約國小二年級設籍）
+• 112學年：設籍滿 4 年（約國小三年級設籍）
+• 113學年：設籍滿 8 年（約幼兒園大班設籍）
+• 114學年：設籍滿 2 年（約國小五年級設籍）
+每年登記人數不同，無法事先保證；一切須待 3/14（六）現場登記後排序才能確定。先比順位、同順位再比設籍先後。</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>新生入學簡報 P.37</t>
+          <t>Q&amp;A Q4；簡報 Q1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -897,30 +918,31 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>改分發</t>
+          <t>設籍計算</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>沒錄取,未錄取,落榜,改分發學校,虎林,成德,光華,育賢,建華</t>
+          <t>累計,搬家,搬遷,學區內遷移,遷出,遷入,金雅里,重算,重新計算,設籍時間怎麼算,設籍日,從哪天算,怎麼算設籍,設籍怎麼算,曾經搬</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>如果沒有被竹光國中錄取，後續會改分發到哪所學校？</t>
+          <t>之前在學區內搬家設籍時間可以累計嗎？中途遷出學區怎麼算？</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>🏫【未錄取改分發規定】：
-1. 【單一學區學生】：依家長意願改分發至「虎林、成德、光華、育賢、建華國中」。（黃單背面有勾選欄）
-2. 【共同學區學生】：改分發至該共同學區之他校。
-本校將於 4/17 前統一函送名冊，改分發國中將於 4/20 前主動寄送入學通知書。</t>
+          <t>🏡【設籍時間計算原則】
+以「學生本人」戶籍遷入學區的時間起算：
+1. 學區內遷移 ➔ 可連續累計：同一學區內里鄰間搬遷（例如境福里 ➔ 民富里），設籍時間得以累計。
+2. 中途遷出學區 ➔ 重新起算：若曾遷出本校學區（例如遷到金雅里）再遷回，則以「最後一次遷入本學區的日期」為設籍日。
+※ 戶籍資料若提供「省略記事」版本，將視為登記當天才入籍，請務必提供含詳細記事的謄本或戶口名簿。</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、七 &amp; 簡報 P.30</t>
+          <t>作業規定伍、二；Q&amp;A Q3；簡報「設籍時間的計算」</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -935,29 +957,36 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>同日遷入</t>
+          <t>現場登記</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>抽籤,雙胞胎,同日設籍,兄姊在校,多胞胎</t>
+          <t>3/14,314,帶什麼,要帶,攜帶,文件,證件,黃單,戶籍謄本,戶口名簿,謄本,登記當天,現場登記,幾點,要本人,本人到,委託,親友代</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>如果最後一名同日遷入如何排序？若是雙胞胎怎麼處理？</t>
+          <t>3/14（六）新生入學現場登記要帶哪些文件？一定要本人到場嗎？</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>👥【同日遷入與多胞胎規定】：
-1. 同日排序：最後一名若有二人以上同日遷入，以【有兄姊就讀本校者為優先】；若條件相同，採【公開抽籤】決定！
-2. 多胞胎手足保障：若最後一名錄取生為多胞胎之一，其多胞胎手足【隨同該生以外加名額就讀本校】！</t>
+          <t>🎒【3/14（六）現場登記應備文件】
+時間：115年3月14日（六）上午 08:00–11:00
+地點：竹光國中
+1. 📄 新生入學通知單（黃單）：背面「入學登記表」與「家訪同意書」填妥並簽名
+2. 👥 戶籍資料（必要，二擇一）：
+   • 三個月內核發之戶籍謄本正本
+   • 新式戶口名簿正本＋影本（須含現住人口及詳細記事；正本驗畢歸還）
+3. 🏠 居住證明（非必要，但影響順位）：自有權狀／115 房屋稅籍證明／公證租約／未公證租約
+※ 可事先備妥資料委託親友到校送件，不一定要家長本人。
+※ 未參加登記者視同放棄入學資格！</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>作業規定伍、四</t>
+          <t>簡報「新生入學登記」Q6/Q7/Q8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -972,30 +1001,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>轉學規定</t>
+          <t>戶籍規定</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>轉入,轉學,學期中,缺額,補實,出國</t>
+          <t>直系,寄居,戶籍不符,爸爸媽媽,爺爺奶奶,阿公阿嬤,外公外婆,監護人,同一戶,同戶,只有小孩,小孩自己,戶籍條件,戶籍要件,一定要戶籍,戶籍一定</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>學期中可以轉學進竹光國中嗎？出國可以保留學籍嗎？</t>
+          <t>學生戶籍內一定要有直系尊親屬同戶嗎？只有小孩設籍可以嗎？</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>🔄【轉出轉入與學期中補實規定】：
-1. 總量限制學校學期中「僅得轉出，不得轉入」！
-2. 學生赴國外就學應辦理轉出，無法辦理保留學籍。
-3. 學期中轉出產生之缺額，一律於【寒假及暑假】公開辦理補實，志願轉入學生依設籍時間先後公開分發。</t>
+          <t>⚠️【戶籍必要條件】
+學生戶籍內「必須至少有一位直系尊親屬或法定監護人」同一戶籍：爸爸、媽媽、爺爺、奶奶、外公、外婆（或法定監護人）。
+若只有學生一人設籍，或寄居在非直系親屬（如叔叔、阿姨）戶內，則【無法參加新生登記，連順位都沒有】。請儘速辦理直系尊親屬遷入。
+※ 兩位以上非兄弟姊妹的新生設籍同一戶籍，學校會進行居住事實查核。</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>作業規定陸、一 &amp; 二</t>
+          <t>作業規定伍、一；Q&amp;A Q7；簡報「入學資格-戶籍」</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1010,32 +1039,38 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>重要時程</t>
+          <t>學區查詢</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>放榜,線上報到,實體報到,學力測驗,考試,重要日程</t>
+          <t>學區,里鄰,哪些里,民富,磐石,北門,境福,新雅,客雅,南勢,中雅,文雅,長和,新民,算不算學區,是學區嗎,在學區內嗎,單一學區,共同學區</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>錄取放榜日與新生報到日期是什麼時候？</t>
+          <t>請問竹光國中的學區有哪些里別？北門里算學區嗎？</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>📅【115重要時程】：
-• 03/23(一) 16:00：公布新生錄取名單（學校首頁及警衛室）
-• 03/30(一)-04/04(六)：正取生【線上報到】
-• 04/07(二)-04/08(三)：正取生實體報到（警衛室）
-• 04/15(三)前：備取遞補報到（電話通知）
-• 05/30(六) 09:00-11:30：新生學力測驗（創意樓，發放暑假作業）</t>
+          <t>🗺️【竹光國中 115學年度學區劃分】
+• 單一學區：民富里、磐石里（全里）、新雅里 1-18 及 20-27 鄰、南勢里 1-6 及 8-9 鄰
+• 共同學區：
+  - 北門里 1-5、7-10、12、13、16、17 鄰 ➔ 竹光／光華／建華（115 新增）
+  - 新雅里 19 鄰 ➔ 竹光／虎林
+  - 南勢里 10 鄰 ➔ 竹光／虎林／成德
+  - 客雅里 1-2 鄰 ➔ 竹光／成德；3-7 鄰 ➔ 竹光／虎林／成德
+  - 境福里 ➔ 竹光／光華
+  - 文雅里 ➔ 竹光／成德／光華
+  - 長和里、新民里 ➔ 竹光／育賢／光華
+  - 中雅里 1-11 鄰 ➔ 竹光／成德；12-16 鄰 ➔ 竹光／虎林／成德
+※ 共同學區與單一學區的排序標準完全一致。以教育處 115 學年度學區劃分表為準。</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>作業規定柒、進度表</t>
+          <t>作業規定肆；簡報「學區範圍」</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1050,35 +1085,232 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>共同學區</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>兩所登記,兩所都,兩校,雙重登記,同時登記,3/12,312,北門里雙登記,也登記光華,也登記建華,也登記虎林,另一所總量</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>北門里是共同學區，可以同時登記竹光國中跟光華國中嗎？</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>⚖️【共同學區同時登記兩所總量管制國中】
+可以！若共同學區內包含另一所總量管制學校（如光華、建華），家長務必於【115年3月12日（四）前】自行向另一所總量國中提出登記申請；逾期將無法同時登記兩校。
+共同學區未獲錄取者，依家長意願改分發至該共同學區之他校。</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>簡報 Q9；作業規定伍、七</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>改分發</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>沒錄取,未錄取,沒有錄取,落榜,沒上,改分發,轉分發,分發到哪,分到哪,去哪間,哪所國中,虎林,成德,育賢,建華,備取,候補</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>如果沒有被竹光國中錄取，後續會改分發到哪所學校？</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>🏫【未錄取改分發規定】
+1. 單一學區學生：依家長意願改分發至「虎林、成德、光華、育賢、建華國中」（黃單背面入學登記表有轉分發勾選欄）。
+2. 共同學區學生：改分發至該共同學區之他校。
+時程：4/15（三）前備取遞補（電話通知）➔ 4/17（一）前本校函送改分發名冊 ➔ 4/20（一）前改分發國中寄送入學通知書 ➔ 5/3（六）一般學校新生報到。
+※ 超出名額者先列備取，有缺額依序遞補。</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>作業規定伍、六～七；簡報 Q3</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>同日遷入</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>抽籤,雙胞胎,同日設籍,同一天,兄姊,哥哥姊姊在,多胞胎,外加名額</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>如果最後一名同日遷入如何排序？雙胞胎怎麼處理？</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>👥【同日遷入與多胞胎規定】
+1. 最後一名若有二人以上同日遷入學區：以【有兄姊就讀本校者優先】；條件相同者採【公開抽籤】決定。
+2. 最後一名錄取學生若為多胞胎之一：其多胞胎手足【隨同該生以外加名額就讀本校】。</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>作業規定伍、四</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>轉學規定</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>轉入,轉學,學期中,缺額,補實,出國,國外,保留學籍,休學,復學,中途</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>學期中可以轉學進竹光國中嗎？出國可以保留學籍嗎？</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>🔄【轉出轉入規定】
+1. 總量限制學校學期中各年級「僅得轉出，不得轉入」（特殊理由經入學審查委員會或市府核准者除外）。
+2. 學生赴國外或大陸地區就學應辦理轉出，無法保留學籍。
+3. 學期中轉出產生的缺額，於【寒假及暑假】辦理補實作業，志願轉入學生按戶籍遷入居住時間先後公開分發。
+4. 中輟生學籍保留原校，得依規定復學。</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>作業規定陸</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>重要時程</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>放榜,公布,公告錄取,錄取名單,線上報到,實體報到,報到,學力測驗,入學測驗,測驗,考試,重要日程,時程,什麼時候,哪一天,幾號,日期</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>錄取放榜日與新生報到日期是什麼時候？</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>📅【115學年度重要時程】
+• 03/06（五）前：透過國小寄發新生入學通知單（黃單）
+• 03/12（四）前：共同學區欲同時登記另一所總量國中者提出申請
+• 03/14（六）08:00–11:00：新生入學現場登記（資格審核）⭐
+• 03/23（一）16:00：公布錄取名冊、候補名冊（註明順位）、未錄取名冊（校網首頁及警衛室）
+• 03/30（一）–04/04（六）：正取生線上報到
+• 04/07（二）–04/08（三）：未線上報到者至警衛室實體報到（擇一即可）
+• 04/15（三）前：缺額候補遞補（電話通知）
+• 04/17（一）前：函送改分發名冊；04/20（一）前改分發國中寄通知
+• 05/30（六）09:00–11:30：新生入學測驗（創意樓，當日發暑假作業）</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>作業規定柒；簡報「重要日程統整」</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>基本資訊</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>幾班,招生人數,地址,電話,分機,註冊組</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>請問今年竹光國中招收幾班？註冊組電話與地址？</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>ℹ️【竹光國中 招生與聯絡資訊】：
-• 核定招生規模：115學年度預計招收 12 班
-• 承辦處室：教務處註冊組
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>幾班,班級數,招生人數,招幾,名額,地址,電話,分機,註冊組,聯絡,人工,真人,找誰問,總量管制是什麼,什麼是總量,總量管制的意思,為什麼要總量,為什麼總量,總量限制是</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>什麼是總量管制？今年招收幾班？註冊組電話與地址？</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ℹ️【竹光國中 115學年度總量管制基本資訊】
+• 什麼是總量管制：本校入學需求遠超過校舍容量，依市府核定實施「班級總量限制」，新生依順位與設籍時間排序錄取，額滿者改分發他校。
+• 核定招生：115學年度預計招收 12 班
+• 承辦單位：教務處註冊組
 • 諮詢專線：(03) 524-6683 分機 613
 • 學校地址：新竹市北區和平路 1 號
 • 官方網站：https://www.zgjh.hc.edu.tw</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>作業規定肆 &amp; 簡報 P.3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>作業規定貳、參；Q&amp;A Q4</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1098,13 +1330,13 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.8" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="38.2" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
     <col width="58" customWidth="1" min="5" max="5"/>
     <col width="18.4" customWidth="1" min="6" max="6"/>
-    <col width="31.59999999999999" customWidth="1" min="7" max="7"/>
+    <col width="31.6" customWidth="1" min="7" max="7"/>
     <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1163,7 +1395,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1.少年保護個案 2.列冊低收入戶子女 3.父母雙亡學童 4.編制內教職員工隨同子女 5.市府安置身障資源生</t>
+          <t>1.少年保護個案 2.列冊低收入戶子女 3.父母雙亡學童 4.本校編制內教職員工子女、受監護人 5.市府鑑定安置之資源生</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1181,14 +1413,14 @@
           <t>須配合家訪</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>依特殊身分法令依序分發</t>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>依特殊身分依序分發</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>除教職員子女外，均會實地查訪居住事實；名單公告後新聘教職員子女得外加。</t>
+          <t>除教職員子女外，均會實地查訪居住事實；名單公告後新聘教職員子女得外加名額。</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1442,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>設籍並實際居住學區內，至少一名直系尊親屬或監護人同戶</t>
+          <t>設籍並實際居住學區內，至少一名直系尊親屬或法定監護人同戶</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>自有：建物所有權狀 或 115房屋稅籍證明；租屋：法院公證租賃契約（涵蓋115/3/14~9/1，承租人為直系尊親屬）</t>
+          <t>自有：建物所有權狀 或 115年度房屋稅籍證明；租屋：法院公證租賃契約（涵蓋115/3/14~9/1，承租人為直系尊親屬）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1223,14 +1455,14 @@
           <t>必須簽具</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>依戶籍遷入學區時間先後排序</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>權狀或租約承租人須為直系尊親屬（父、母、祖父母、外祖父母）名下。</t>
+          <t>權狀或租約承租人須為直系尊親屬（父、母、祖父母、外祖父母）或法定監護人名下。自有與公證租約排序效力相同。</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1489,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>自有：建物所有權狀 或 115房屋稅籍證明；租屋：法院公證租賃契約（涵蓋115/3/14~9/1）</t>
+          <t>自有：建物所有權狀 或 115年度房屋稅籍證明；租屋：法院公證租賃契約（涵蓋115/3/14~9/1）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1265,7 +1497,7 @@
           <t>必須簽具</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>依戶籍遷入學區時間先後排序</t>
         </is>
@@ -1284,12 +1516,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>本學區國小畢業生 × 未公證租約</t>
+          <t>戶籍符合 × 未公證租約</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>設籍本學區之國民小學應屆畢業生</t>
+          <t>設籍本學區之國民小學應屆畢業生（不分本市／外縣市）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1307,14 +1539,14 @@
           <t>必須簽具</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>依戶籍遷入學區時間先後排序</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>115重大新增/修訂順位！無公證租約者不必恐慌，仍可名列第四順位。</t>
+          <t>115 新增順位。租約補辦公證即可提升為第二（或第三）順位。</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1558,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>本學區國小畢業生 × 無居住證明</t>
+          <t>戶籍符合 × 無居住證明</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>設籍本學區之國民小學應屆畢業生</t>
+          <t>設籍本學區之國民小學應屆畢業生（不分本市／外縣市）</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1341,7 +1573,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>無法提供居住證明文件（或居住文件不符規定者）</t>
+          <t>無法提供居住證明文件（沒有權狀、沒有租約），或居住文件不符規定者</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1349,21 +1581,21 @@
           <t>必須簽具</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>依戶籍遷入學區時間先後排序</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>只要戶籍符合（有直系同戶），即便無居住證明仍列第五順位。</t>
+          <t>只要戶籍符合（有直系同戶）並簽家訪同意書，即便無任何居住證明仍列第五順位。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>最後順位</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>第六順位（最後順位）</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1373,7 +1605,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>符合入學資格，但無法簽具家訪同意書者，或經查訪為非實際居住/空戶</t>
+          <t>符合入學資格但無法簽具家訪同意書者；或經查訪為已遷居學區外、非實際居住、空戶者</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1381,9 +1613,9 @@
           <t>設籍本學區</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>未提供或不符</t>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>不論有無</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1391,14 +1623,14 @@
           <t>無法簽具或拒簽</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>列於最末順位錄取</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>若經查訪為空戶或非實際居住，列最後順位並勸導勒令轉入實際學區。若戶籍無直系同戶則無順位。</t>
+          <t>空戶或非實際居住者列第六順位並勸導轉入實際居住學區學校。※ 戶籍內無直系尊親屬同戶者無法登記，連順位都沒有。</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1645,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11.8" customWidth="1" min="2" max="2"/>
     <col width="11.8" customWidth="1" min="3" max="3"/>
     <col width="32.7" customWidth="1" min="4" max="4"/>
-    <col width="21.7" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
     <col width="28.3" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1483,7 +1715,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>無 (竹光單一學區)</t>
+          <t>無（竹光單一學區）</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1491,7 +1723,7 @@
           <t>依家長意願改分發：虎林、成德、光華、育賢、建華國中</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>竹光核心單一學區</t>
         </is>
@@ -1518,7 +1750,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>無 (竹光單一學區)</t>
+          <t>無（竹光單一學區）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1526,7 +1758,7 @@
           <t>依家長意願改分發：虎林、成德、光華、育賢、建華國中</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>竹光核心單一學區</t>
         </is>
@@ -1553,7 +1785,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>無 (竹光單一學區)</t>
+          <t>無（竹光單一學區）</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1561,7 +1793,7 @@
           <t>依家長意願改分發：虎林、成德、光華、育賢、建華國中</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>19鄰除外</t>
         </is>
@@ -1573,32 +1805,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>共同學區</t>
+          <t>單一學區</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>北門里</t>
+          <t>南勢里</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1-5、7-10、12、13、16、17鄰</t>
+          <t>1-6鄰、8-9鄰</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>竹光、光華、建華</t>
+          <t>無（竹光單一學區）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>依家長意願改分發至光華或建華國中</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>115學年度新增共同學區！</t>
+          <t>依家長意願改分發：虎林、成德、光華、育賢、建華國中</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>作業規定肆、四</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1845,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>新雅里</t>
+          <t>南勢里</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19鄰</t>
+          <t>10鄰</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>竹光、虎林</t>
+          <t>竹光、虎林、成德</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>改分發至虎林國中</t>
+          <t>依家長意願改分發至虎林國中或成德高中(國中部)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1648,27 +1880,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>南勢里</t>
+          <t>北門里</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1-6鄰、8-9鄰、10鄰</t>
+          <t>1-5、7-10、12、13、16、17鄰</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>竹光、虎林、成德</t>
+          <t>竹光、光華、建華</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>依家長意願改分發至虎林國中或成德高中(國中部)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>共同學區</t>
+          <t>依家長意願改分發至光華或建華國中</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>115學年度新增共同學區！</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1915,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>客雅里</t>
+          <t>新雅里</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1-2鄰</t>
+          <t>19鄰</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>竹光、成德</t>
+          <t>竹光、虎林</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>改分發至成德高中(國中部)</t>
+          <t>改分發至虎林國中</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1723,17 +1955,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3-7鄰</t>
+          <t>1-2鄰</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>竹光、虎林、成德</t>
+          <t>竹光、成德</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>依家長意願改分發至虎林或成德</t>
+          <t>改分發至成德高中(國中部)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1753,22 +1985,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>境福里</t>
+          <t>客雅里</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>全里</t>
+          <t>3-7鄰</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>竹光、光華</t>
+          <t>竹光、虎林、成德</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>改分發至光華國中</t>
+          <t>依家長意願改分發至虎林或成德</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1788,7 +2020,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>文雅里</t>
+          <t>境福里</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1798,12 +2030,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>竹光、成德、光華</t>
+          <t>竹光、光華</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>依家長意願改分發至成德或光華國中</t>
+          <t>改分發至光華國中</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1823,7 +2055,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>長和里</t>
+          <t>文雅里</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1833,12 +2065,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>竹光、育賢、光華</t>
+          <t>竹光、成德、光華</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>依家長意願改分發至育賢或光華國中</t>
+          <t>依家長意願改分發至成德或光華國中</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1858,7 +2090,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>新民里</t>
+          <t>長和里</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1893,22 +2125,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中雅里</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>1-11鄰</t>
+          <t>新民里</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>全里</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>竹光、成德</t>
+          <t>竹光、育賢、光華</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>改分發至成德高中(國中部)</t>
+          <t>依家長意願改分發至育賢或光華國中</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1933,20 +2165,55 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t>1-11鄰</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>竹光、成德</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>改分發至成德高中(國中部)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>共同學區</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>共同學區</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>中雅里</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>12-16鄰</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>竹光、虎林、成德</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>依家長意願改分發至虎林或成德</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>共同學區</t>
         </is>
@@ -1968,7 +2235,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="28.3" customWidth="1" min="2" max="2"/>
-    <col width="32.70000000000001" customWidth="1" min="3" max="3"/>
+    <col width="32.7" customWidth="1" min="3" max="3"/>
     <col width="22.8" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
@@ -2006,7 +2273,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -2036,7 +2303,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -2066,7 +2333,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -2080,9 +2347,9 @@
           <t>115.02.26 (四)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>竹光國中活動中心</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>竹光國中</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2092,11 +2359,11 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>向國小端與學區家長詳細說明總量管制與審查要點。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>向國小端與學區家長說明總量管制與審查要點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2126,7 +2393,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -2152,11 +2419,11 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>寄發黃單（正面入學資格單與規定，背面登記表及家訪同意書）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+          <t>黃單正面：入學資格通知單＋作業規定；背面：入學登記表＋家訪同意書。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -2182,11 +2449,11 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>若共同學區欲同時登記另一所總量國中，家長須於3/12前提出申請！</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
+          <t>共同學區欲同時登記另一所總量國中，家長須於 3/12 前提出申請。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -2212,11 +2479,11 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>重要！攜帶黃單、全戶謄本/名簿正影本、居住證明。未登記者視同放棄！</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+          <t>攜帶黃單、戶籍謄本或戶口名簿正影本、居住證明。未登記者視同放棄！</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -2246,7 +2513,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -2272,17 +2539,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>公布錄取名冊、候補名冊（註明順位）與未錄取名冊。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+          <t>公布錄取名冊、候補名冊（註明順位）與未錄取名冊（註明改分發學校）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>正取生 線上報到 ⭐</t>
+          <t>正取生線上報到 ⭐</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2302,17 +2569,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>正取生可線上完成報到，免親自到校。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
+          <t>線上報到或實體報到擇一即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>正取生 實體報到</t>
+          <t>正取生實體報到</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2332,11 +2599,11 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>未於線上報到者，請至警衛室填寫實體報到資料。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
+          <t>未於線上報到者，至警衛室填寫實體報到資料。未報到視同放棄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2355,18 +2622,18 @@
           <t>電訪/家訪</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>註冊組/生教組</t>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>註冊組</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>針對未報到之正取生進行電話追蹤與訪視確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
+          <t>針對未報到之正取生進行追蹤確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2392,11 +2659,11 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>依候補名冊序位，以電話依序通知備取生到校辦理遞補報到。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
+          <t>依候補名冊序位電話通知備取生到校辦理遞補報到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2422,11 +2689,11 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>將未錄取學生名冊依家長志願正式函送至虎林、成德、光華等校。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
+          <t>將未錄取學生名冊依家長志願函送至各改分發國中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2452,11 +2719,11 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>各改分發國中寄送新生入學通知書給轉分發學生。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
+          <t>由改分發國中寄送新生入學通知書。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2482,17 +2749,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>改分發學生至該校辦理報到（本校正取生已於4/8前報到完畢）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
+          <t>本校正取生已於 4/8 前完成報到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>新生入學學力測驗 ⭐</t>
+          <t>新生入學測驗 ⭐</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2505,14 +2772,14 @@
           <t>竹光國中創意樓</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>教務處教學組/註冊組</t>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>教務處</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>新生全體參加入學測驗，當日發放暑假作業與各類營隊通知。</t>
+          <t>當日發放暑假作業與營隊通知；考場當日公告。</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2798,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16.2" customWidth="1" min="2" max="2"/>
+    <col width="17.3" customWidth="1" min="2" max="2"/>
     <col width="22.8" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
@@ -2566,12 +2833,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>錄取情況與大數據分析說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+          <t>錄取情況說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>111 學年度</t>
         </is>
@@ -2602,8 +2869,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>112 學年度</t>
         </is>
@@ -2630,12 +2897,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>112學年新生人數略降，第四順位設籍滿4年者全數錄取。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+          <t>112學年第四順位設籍滿4年者錄取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>113 學年度</t>
         </is>
@@ -2657,17 +2924,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>約幼兒園大班前設籍</t>
+          <t>約幼兒園大班設籍</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>龍年效應或學區適齡人口高峰，第四順位設籍門檻高達8年。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+          <t>113學年學區適齡人口高峰，第四順位設籍門檻達8年。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>114 學年度</t>
         </is>
@@ -2694,19 +2961,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>114學年招生穩定，第四順位設籍滿2年即順利錄取。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+          <t>114學年第四順位設籍滿2年即錄取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>115 學年度</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12 班 (預計)</t>
+          <t>12 班（預計）</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2726,7 +2993,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>115學年新增北門里共同學區，核定12班，實際門檻待3/23放榜公告。</t>
+          <t>115學年新增北門里共同學區；實際門檻待 3/23 放榜公告。</t>
         </is>
       </c>
     </row>
@@ -2741,17 +3008,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.9" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16.2" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="1" max="1"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="18.4" customWidth="1" min="3" max="3"/>
     <col width="16.2" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
-    <col width="29.4" customWidth="1" min="7" max="7"/>
-    <col width="31.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="16.2" customWidth="1" min="5" max="5"/>
+    <col width="20.6" customWidth="1" min="6" max="6"/>
+    <col width="11.8" customWidth="1" min="7" max="7"/>
+    <col width="16.2" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2767,7 +3034,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>家長LINE暱稱</t>
+          <t>家長LINE識別碼</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2787,96 +3054,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>處理狀態 (待查覆/已結案)</t>
+          <t>處理狀態</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>承辦同仁備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026/03/10 14:25:10</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Q115031001</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>王小明爸爸</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>民富國小</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>請問我們租約剛去法院公證，但租期只簽到8月31日，可以算第二順位嗎？</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>告知租期須涵蓋至9月1日開學日，建議儘速請房東協議補正至9/1。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>已結案</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>電話已向家長確認合約展期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026/03/11 09:12:45</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Q115031102</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>林媽媽</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>北門國小</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>北門里115年是共同學區，我想竹光跟光華都去登記，請問最晚什麼時候要申請？</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>說明須於3/12前自行向光華國中提出雙重登記申請。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>已結案</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>LINE機器人自動即時回答。</t>
         </is>
       </c>
     </row>
@@ -2891,16 +3074,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.9" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="16.2" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="1" max="1"/>
+    <col width="16.2" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
     <col width="16.2" customWidth="1" min="4" max="4"/>
     <col width="11.8" customWidth="1" min="5" max="5"/>
     <col width="16.2" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="22.8" customWidth="1" min="7" max="7"/>
     <col width="18.4" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -2946,46 +3129,6 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026/03/08 20:15:30</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>請問外公的房子但是外公已經過世還沒辦完繼承登記，權狀算直系自有嗎？</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>家長諮詢模式</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>U847291048</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>教務處註冊組</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>須檢附國稅局遺產稅申報證明或戶政繼承證明佐證直系親屬繼承事實。</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>評估中</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/竹光國中115學年度總量管制知識庫.xlsx
+++ b/竹光國中115學年度總量管制知識庫.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1311,6 +1311,47 @@
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>順位判定</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>租房,租屋,租的,承租,房東,租賃,租約,-公證,-沒有租約,-沒租約,-無租約,-沒有租賃,-沒有租屋證明</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>我們是租房子的，算第幾順位？</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>🏠【租屋家庭順位速查】
+租屋者只要戶籍符合（學生設籍學區＋直系尊親屬同戶）都可以登記，順位看租約狀態：
+• 有「法院公證」租約 ➔ 第二順位（外縣市國小畢業為第三順位）
+• 只有「未公證」租約 ➔ 第四順位
+• 沒有租約／租約不符規定 ➔ 第五順位
+租約條件：租期涵蓋 115/3/14～115/9/1，承租人須為學生的直系尊親屬或法定監護人。
+再告訴我「有公證」「沒公證」或「沒有租約」，我幫您精確判定！</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>作業規定伍、三、2～5；Q&amp;A Q8</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/竹光國中115學年度總量管制知識庫.xlsx
+++ b/竹光國中115學年度總量管制知識庫.xlsx
@@ -529,17 +529,19 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>📚【115學年度竹光國中 錄取順位總覽】
-━━━━━━━━━━━━━━
-先決條件：學生設籍並實際居住學區內，且戶籍內至少有一位直系尊親屬（父母／祖父母／外祖父母）或法定監護人同戶。戶籍不符者連順位都沒有。
-• 第一順位：少年保護個案、列冊低收入戶子女、父母雙亡學童、本校編制內教職員工子女、市府鑑定安置之資源生
-• 第二順位：新竹市國小畢業生＋完整居住證明（自有權狀／115房屋稅籍證明，或法院公證租約）＋家訪同意書
-• 第三順位：外縣市國小畢業生＋完整居住證明＋家訪同意書
-• 第四順位：僅提供「未經法院公證」的租約（租期涵蓋 115/3/14～9/1）＋家訪同意書
-• 第五順位：戶籍符合但無法提供居住證明（或文件不符規定）＋家訪同意書
-• 第六順位（最後順位）：無法簽具家訪同意書，或經查為空戶／非實際居住者
-排序規則：先比順位，同順位再比戶籍遷入學區時間先後。
-想知道自己是第幾順位？直接輸入「我有權狀」「租約沒公證」「沒有租約」等描述即可試算！</t>
+          <t>📚 結果：竹光國中 115 學年度共有六個順位
+🥇 第一順位：少年保護個案、列冊低收入戶子女、父母雙亡學童、本校教職員子女、市府安置資源生
+🥈 第二順位：新竹市國小畢業＋自有權狀（或 115 房屋稅籍證明）或法院公證租約
+🥉 第三順位：外縣市國小畢業＋自有權狀或法院公證租約
+4️⃣ 第四順位：只有「未經法院公證」的租約
+5️⃣ 第五順位：戶籍符合，但沒有任何居住證明
+6️⃣ 第六順位（最後順位）：不簽家訪同意書，或經查為空戶
+📋 原因與規則
+• 先決條件：學生設籍並實際居住學區內，且戶籍內有直系尊親屬（父母／祖父母／外祖父母）或法定監護人同戶
+• 戶籍不符者無法登記，連順位都沒有
+• 排序：先比順位，同順位再比戶籍遷入學區的時間先後
+• 第二到第五順位都要簽家訪同意書
+💡 想知道自己第幾順位，直接輸入「我有權狀」「租約沒公證」「沒有租約」試算</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -574,14 +576,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>🥇【第一順位：法定特殊身分】
-依 115 作業規定，下列身分且設籍本校學區者列為第一順位：
-1. 經縣市政府轉介安置之少年保護個案
-2. 設籍本市且居住學區內、經市府列冊之低收入戶子女
-3. 設籍本市且居住學區內而父母雙亡者
-4. 本校現職編制內教職員工之子女、受監護人（隨父母或監護人就讀所服務學校；名單公告後新聘者採外加名額）
-5. 經市府鑑定並安置之資源生
-※ 除教職員子女外，學校會實地訪查是否有居住事實。</t>
+          <t>🥇 結果：第一順位
+📋 適用身分（設籍本校學區者）
+• 經縣市政府轉介安置的少年保護個案
+• 設籍本市且居住學區內、經市府列冊的低收入戶子女
+• 設籍本市且居住學區內而父母雙亡者
+• 本校現職編制內教職員工的子女、受監護人（隨父母或監護人就讀所服務學校）
+• 經市府鑑定並安置的資源生
+📌 說明
+• 依 115 作業規定伍、三、1
+• 除教職員子女外，學校會實地訪查是否有居住事實
+• 名單公告後新聘的教職員子女採外加名額</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -616,11 +621,15 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>🎯【判定結果：第二順位（本市國小）／第三順位（外縣市國小）】
-依 115 作業規定：設籍並實際居住本校學區內、戶籍與直系尊親屬同戶，檢附「登記於直系尊親屬或法定監護人名下」的房屋所有權狀（或 115 年度房屋稅籍證明），並簽具家訪同意書者：
-• 新竹市國小應屆畢業生 ➔【第二順位】
-• 外縣市國小應屆畢業生 ➔【第三順位】
-※ 自有住宅與公證租約在排序上完全相同，都是第二（或第三）順位。</t>
+          <t>🎯 結果：第二順位（新竹市國小畢業）／第三順位（外縣市國小畢業）
+📋 原因
+• 學生設籍並實際居住本校學區，且與直系尊親屬同戶
+• 房屋所有權狀（或 115 年度房屋稅籍證明）登記在直系尊親屬或法定監護人名下
+• 簽具家訪同意書
+📌 說明
+• 依 115 作業規定伍、三、2 及 3
+• 自有住宅與法院公證租約排序效力相同
+• 同順位再比戶籍遷入學區時間先後</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -655,11 +664,15 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>⚖️【判定結果：第二順位（本市）／第三順位（外縣市）】
-租屋家庭若能提供「經法院公證之房屋租賃契約」（租賃期間須涵蓋 115/3/14 新生登記日至 115/9/1 開學日，承租人須為學生的直系尊親屬或法定監護人），並簽具家訪同意書：
-• 新竹市國小畢業生 ➔【第二順位】
-• 外縣市國小畢業生 ➔【第三順位】
-公證租約與自有權狀在排序上效力相同。</t>
+          <t>⚖️ 結果：第二順位（新竹市國小畢業）／第三順位（外縣市國小畢業）
+📋 原因
+• 有「經法院公證」的房屋租賃契約
+• 租期涵蓋 115/3/14 新生登記日至 115/9/1 開學日
+• 承租人是學生的直系尊親屬或法定監護人
+• 簽具家訪同意書
+📌 說明
+• 依 115 作業規定伍、三、2 及 3；Q&amp;A 第 8 題
+• 公證租約與自有權狀排序效力相同</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -694,10 +707,16 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>📋【判定結果：第四順位】
-依 115 作業規定：只要戶籍符合（設籍學區且與直系尊親屬同戶），就可以參加新生登記！
-若僅能提供「未經法院公證的房屋租賃契約」（租期須涵蓋 115/3/14～115/9/1，承租人為直系尊親屬），並簽具家訪同意書，列為【第四順位】。
-💡 提示：若能在 3/14 登記前補辦法院公證，即可提升為第二順位（外縣市國小為第三順位）。</t>
+          <t>📋 結果：第四順位
+📋 原因
+• 戶籍符合（學生設籍學區，且與直系尊親屬同戶），可以參加新生登記
+• 只有「未經法院公證」的房屋租賃契約
+• 租期涵蓋 115/3/14 至 115/9/1，承租人為直系尊親屬
+• 簽具家訪同意書
+📌 說明
+• 依 115 作業規定伍、三、4；Q&amp;A 第 8 題
+• 同順位再比戶籍遷入學區時間先後
+💡 提示：3/14 登記前補辦法院公證，可提升為第二順位（外縣市國小為第三順位）</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -732,11 +751,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>📌【判定結果：第五順位】
-依 115 作業規定：只要戶籍符合（學生設籍學區，且戶籍內有直系尊親屬或法定監護人同戶），即使無法提供任何居住證明文件（沒有權狀、沒有租約），或提供的文件不符規定（例如承租人不是直系尊親屬、租期未涵蓋 3/14～9/1），只要簽具家訪同意書，仍可列為【第五順位】參加排序。
-💡 想提升順位：
-• 補一份「未公證」租約（租期涵蓋 115/3/14～9/1、承租人為直系尊親屬）➔ 第四順位
-• 租約再去法院公證 ➔ 第二順位（外縣市國小為第三順位）</t>
+          <t>📌 結果：第五順位
+📋 原因
+• 戶籍符合：學生設籍學區，且戶籍內有直系尊親屬或法定監護人同戶
+• 沒有任何居住證明（沒有權狀、沒有租約），或文件不符規定（承租人不是直系尊親屬、租期未涵蓋 3/14 至 9/1）
+• 簽具家訪同意書即可參加排序
+📌 說明
+• 依 115 作業規定伍、三、5
+• 同順位再比戶籍遷入學區時間先後
+💡 想提升順位
+• 補一份「未公證」租約（租期涵蓋 115/3/14 至 9/1、承租人為直系尊親屬）→ 第四順位
+• 租約再去法院公證 → 第二順位（外縣市國小為第三順位）</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -771,13 +796,15 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>🔍【第二／第四／第五順位 差別一次看懂】
-三者戶籍條件都一樣（設籍學區＋直系尊親屬同戶＋簽家訪同意書），差別只在「居住證明文件」：
-• 第二順位（外縣市國小為第三）：有「完整」居住證明 ➔ 自有房屋所有權狀／115 房屋稅籍證明，或「經法院公證」的租約
-• 第四順位：只有「未經法院公證」的租約（租期涵蓋 115/3/14～9/1，承租人為直系尊親屬）
+          <t>🔍 結果：差別只在「居住證明文件」，戶籍條件完全一樣
+📋 三者對照
+• 第二順位：有完整居住證明，也就是自有權狀（或 115 房屋稅籍證明）或「法院公證」租約（外縣市國小畢業為第三順位）
+• 第四順位：只有「未經法院公證」的租約（租期涵蓋 115/3/14 至 9/1，承租人為直系尊親屬）
 • 第五順位：完全沒有居住證明（沒權狀、沒租約），或文件不符規定
-一句話：有公證租約＝第二、租約沒公證＝第四、連租約都沒有＝第五。
-同一順位內再依戶籍遷入學區時間先後排序。</t>
+📌 說明
+• 三者都要：學生設籍學區＋直系尊親屬同戶＋簽家訪同意書
+• 一句話：有公證租約是第二，租約沒公證是第四，連租約都沒有是第五
+• 同順位再比戶籍遷入學區時間先後（依 115 作業規定伍、三、2 至 5）</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -812,12 +839,15 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>⚠️【第六順位（最後順位）】
-依 115 作業規定，下列情形列為第六順位（最後順位）錄取：
-1. 符合入學資格，但無法簽具（或不同意）家訪同意書者
-2. 經學校訪查發現已遷居學區外、非實際居住或為「空戶」（人籍分離）者 ➔ 列第六順位並勸導轉入實際居住學區的學校
-※ 家訪同意書在黃單背面，請務必簽名；學校得視需求不定期查核居住事實。
-※ 若戶籍內沒有直系尊親屬同戶，則「無法參加新生登記」，連順位都沒有（這不是第六順位）。</t>
+          <t>⚠️ 結果：第六順位（最後順位）
+📋 適用情形
+• 符合入學資格，但無法簽具（或不同意）家訪同意書
+• 經學校訪查已遷居學區外、非實際居住，或為空戶（人籍分離）
+📌 說明
+• 依 115 作業規定伍、三、6 及伍、五
+• 家訪同意書在黃單背面，請務必簽名；學校得不定期查核居住事實
+• 空戶者列第六順位並勸導轉入實際居住學區的學校
+• 戶籍內沒有直系尊親屬同戶者「無法登記」，連順位都沒有（這不是第六順位）</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -852,13 +882,17 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>📐【錄取排序原則】
-1. 先比「順位」：第一順位全部排完，才輪到第二順位，依此類推。
-2. 同順位再比「戶籍遷入學區時間」：越早設籍越優先。
-3. 最後一名若有二人以上同日遷入：有兄姊就讀本校者優先；條件相同則公開抽籤。
-4. 最後一名若為多胞胎之一：其多胞胎手足以外加名額隨同就讀。
-5. 超出核定名額者依序列為備取。
-※ 共同學區與單一學區的排序基準完全一樣；自有住宅與公證租約也一樣（皆第二順位）。</t>
+          <t>📐 結果：先比順位，同順位再比戶籍遷入學區的時間
+📋 排序規則
+• 第一順位全部排完，才輪到第二順位，依此類推
+• 同順位者，越早設籍越優先
+• 最後一名若有二人以上同日遷入：有兄姊就讀本校者優先；條件相同則公開抽籤
+• 最後一名若為多胞胎之一：其多胞胎手足以外加名額隨同就讀
+• 超出核定名額者依序列為備取
+📌 說明
+• 依 115 作業規定伍、四
+• 共同學區與單一學區排序基準完全一樣
+• 自有住宅與公證租約排序效力一樣（都是第二順位）</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -893,12 +927,15 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>📊【歷年第四順位設籍門檻參考】
-• 111學年：設籍滿 5 年（約國小二年級設籍）
-• 112學年：設籍滿 4 年（約國小三年級設籍）
-• 113學年：設籍滿 8 年（約幼兒園大班設籍）
-• 114學年：設籍滿 2 年（約國小五年級設籍）
-每年登記人數不同，無法事先保證；一切須待 3/14（六）現場登記後排序才能確定。先比順位、同順位再比設籍先後。</t>
+          <t>📊 結果：無法事先保證，要等 3/14（六）登記後排序才知道
+📋 歷年第四順位設籍門檻參考
+• 111 學年：設籍滿 5 年（約小二設籍）
+• 112 學年：設籍滿 4 年（約小三設籍）
+• 113 學年：設籍滿 8 年（約大班設籍）
+• 114 學年：設籍滿 2 年（約小五設籍）
+📌 說明
+• 每年登記人數不同，門檻隨之浮動
+• 先比順位，同順位再比設籍先後（Q&amp;A 第 4 題；說明會 Q1）</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -933,11 +970,14 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>🏡【設籍時間計算原則】
-以「學生本人」戶籍遷入學區的時間起算：
-1. 學區內遷移 ➔ 可連續累計：同一學區內里鄰間搬遷（例如境福里 ➔ 民富里），設籍時間得以累計。
-2. 中途遷出學區 ➔ 重新起算：若曾遷出本校學區（例如遷到金雅里）再遷回，則以「最後一次遷入本學區的日期」為設籍日。
-※ 戶籍資料若提供「省略記事」版本，將視為登記當天才入籍，請務必提供含詳細記事的謄本或戶口名簿。</t>
+          <t>🏡 結果：學區內搬家可累計；曾遷出學區則從最後一次遷入日重算
+📋 計算原則
+• 以「學生本人」戶籍遷入學區的時間起算
+• 同一學區內里鄰間搬遷（例如境福里到民富里），設籍時間可以累計
+• 中途遷出本校學區（例如遷到金雅里）再遷回，以最後一次遷入本學區的日期為設籍日
+📌 說明
+• 依 115 作業規定伍、二；Q&amp;A 第 3 題
+• 戶籍資料若提供「省略記事」版本，會視為登記當天才入籍，請提供含詳細記事的謄本或戶口名簿</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -972,16 +1012,17 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>🎒【3/14（六）現場登記應備文件】
-時間：115年3月14日（六）上午 08:00–11:00
-地點：竹光國中
-1. 📄 新生入學通知單（黃單）：背面「入學登記表」與「家訪同意書」填妥並簽名
-2. 👥 戶籍資料（必要，二擇一）：
-   • 三個月內核發之戶籍謄本正本
-   • 新式戶口名簿正本＋影本（須含現住人口及詳細記事；正本驗畢歸還）
-3. 🏠 居住證明（非必要，但影響順位）：自有權狀／115 房屋稅籍證明／公證租約／未公證租約
-※ 可事先備妥資料委託親友到校送件，不一定要家長本人。
-※ 未參加登記者視同放棄入學資格！</t>
+          <t>🎒 結果：帶黃單、戶籍資料、居住證明；不一定要本人到場
+📅 時間地點
+• 115 年 3 月 14 日（六）上午 08:00 至 11:00
+• 竹光國中
+📋 應備文件
+• 新生入學通知單（黃單）：背面「入學登記表」與「家訪同意書」填妥並簽名
+• 戶籍資料（必要，二擇一）：三個月內戶籍謄本正本；或新式戶口名簿正本＋影本（須含現住人口及詳細記事，正本驗畢歸還）
+• 居住證明（非必要，但影響順位）：自有權狀／115 房屋稅籍證明／公證租約／未公證租約
+📌 說明
+• 可備妥資料委託親友到校送件
+• 未參加登記者視同放棄入學資格（說明會 Q6 至 Q8）</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1016,10 +1057,14 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>⚠️【戶籍必要條件】
-學生戶籍內「必須至少有一位直系尊親屬或法定監護人」同一戶籍：爸爸、媽媽、爺爺、奶奶、外公、外婆（或法定監護人）。
-若只有學生一人設籍，或寄居在非直系親屬（如叔叔、阿姨）戶內，則【無法參加新生登記，連順位都沒有】。請儘速辦理直系尊親屬遷入。
-※ 兩位以上非兄弟姊妹的新生設籍同一戶籍，學校會進行居住事實查核。</t>
+          <t>⚠️ 結果：一定要有直系尊親屬同戶；只有小孩設籍無法登記
+📋 規定
+• 學生戶籍內至少要有一位直系尊親屬或法定監護人：爸爸、媽媽、爺爺、奶奶、外公、外婆
+• 只有學生一人設籍，或寄居非直系親屬（叔叔、阿姨）戶內，無法參加新生登記，連順位都沒有
+📌 說明
+• 依 115 作業規定伍、一；Q&amp;A 第 7 題
+• 請儘速辦理直系尊親屬遷入
+• 兩位以上非兄弟姊妹的新生設籍同一戶，學校會進行居住事實查核</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1054,18 +1099,23 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>🗺️【竹光國中 115學年度學區劃分】
-• 單一學區：民富里、磐石里（全里）、新雅里 1-18 及 20-27 鄰、南勢里 1-6 及 8-9 鄰
-• 共同學區：
-  - 北門里 1-5、7-10、12、13、16、17 鄰 ➔ 竹光／光華／建華（115 新增）
-  - 新雅里 19 鄰 ➔ 竹光／虎林
-  - 南勢里 10 鄰 ➔ 竹光／虎林／成德
-  - 客雅里 1-2 鄰 ➔ 竹光／成德；3-7 鄰 ➔ 竹光／虎林／成德
-  - 境福里 ➔ 竹光／光華
-  - 文雅里 ➔ 竹光／成德／光華
-  - 長和里、新民里 ➔ 竹光／育賢／光華
-  - 中雅里 1-11 鄰 ➔ 竹光／成德；12-16 鄰 ➔ 竹光／虎林／成德
-※ 共同學區與單一學區的排序標準完全一致。以教育處 115 學年度學區劃分表為準。</t>
+          <t>🗺️ 結果：竹光國中 115 學年度學區如下
+📋 單一學區
+• 民富里、磐石里（全里）
+• 新雅里 1 至 18 鄰、20 至 27 鄰
+• 南勢里 1 至 6 鄰、8 至 9 鄰
+📋 共同學區
+• 北門里 1 至 5、7 至 10、12、13、16、17 鄰：竹光／光華／建華（115 新增）
+• 新雅里 19 鄰：竹光／虎林
+• 南勢里 10 鄰：竹光／虎林／成德
+• 客雅里 1 至 2 鄰：竹光／成德；3 至 7 鄰：竹光／虎林／成德
+• 境福里：竹光／光華
+• 文雅里：竹光／成德／光華
+• 長和里、新民里：竹光／育賢／光華
+• 中雅里 1 至 11 鄰：竹光／成德；12 至 16 鄰：竹光／虎林／成德
+📌 說明
+• 依 115 作業規定肆；以教育處 115 學年度學區劃分表為準
+• 共同學區與單一學區排序標準完全一致</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1100,9 +1150,13 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>⚖️【共同學區同時登記兩所總量管制國中】
-可以！若共同學區內包含另一所總量管制學校（如光華、建華），家長務必於【115年3月12日（四）前】自行向另一所總量國中提出登記申請；逾期將無法同時登記兩校。
-共同學區未獲錄取者，依家長意願改分發至該共同學區之他校。</t>
+          <t>⚖️ 結果：可以，但要在 115 年 3 月 12 日（四）前自行向另一所總量國中申請
+📋 規定
+• 共同學區若包含另一所總量管制學校（如光華、建華），家長可兩校都登記
+• 須於 3/12 前向另一所總量國中提出登記申請，逾期無法同時登記
+• 共同學區未獲錄取者，依家長意願改分發至該共同學區的他校
+📌 說明
+• 依說明會 Q9；115 作業規定伍、七</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1137,11 +1191,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>🏫【未錄取改分發規定】
-1. 單一學區學生：依家長意願改分發至「虎林、成德、光華、育賢、建華國中」（黃單背面入學登記表有轉分發勾選欄）。
-2. 共同學區學生：改分發至該共同學區之他校。
-時程：4/15（三）前備取遞補（電話通知）➔ 4/17（一）前本校函送改分發名冊 ➔ 4/20（一）前改分發國中寄送入學通知書 ➔ 5/3（六）一般學校新生報到。
-※ 超出名額者先列備取，有缺額依序遞補。</t>
+          <t>🏫 結果：依家長意願改分發
+📋 改分發學校
+• 單一學區學生：虎林、成德、光華、育賢、建華國中（黃單背面入學登記表有轉分發勾選欄）
+• 共同學區學生：該共同學區的他校
+📅 時程
+• 4/15（三）前：備取遞補（電話通知）
+• 4/17（一）前：本校函送改分發名冊
+• 4/20（一）前：改分發國中寄送入學通知書
+• 5/3（六）：一般學校新生報到
+📌 說明
+• 依 115 作業規定伍、六至七；說明會 Q3
+• 超出名額者先列備取，有缺額依序遞補</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1176,9 +1237,13 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>👥【同日遷入與多胞胎規定】
-1. 最後一名若有二人以上同日遷入學區：以【有兄姊就讀本校者優先】；條件相同者採【公開抽籤】決定。
-2. 最後一名錄取學生若為多胞胎之一：其多胞胎手足【隨同該生以外加名額就讀本校】。</t>
+          <t>👥 結果：同日遷入先看兄姊，再抽籤；多胞胎手足外加名額
+📋 規定
+• 最後一名若有二人以上同日遷入學區：有兄姊就讀本校者優先
+• 條件相同者：公開抽籤決定
+• 最後一名錄取學生若為多胞胎之一：其多胞胎手足隨同該生以外加名額就讀本校
+📌 說明
+• 依 115 作業規定伍、四</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1213,11 +1278,14 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>🔄【轉出轉入規定】
-1. 總量限制學校學期中各年級「僅得轉出，不得轉入」（特殊理由經入學審查委員會或市府核准者除外）。
-2. 學生赴國外或大陸地區就學應辦理轉出，無法保留學籍。
-3. 學期中轉出產生的缺額，於【寒假及暑假】辦理補實作業，志願轉入學生按戶籍遷入居住時間先後公開分發。
-4. 中輟生學籍保留原校，得依規定復學。</t>
+          <t>🔄 結果：學期中只能轉出、不能轉入；出國不能保留學籍
+📋 規定
+• 總量限制學校學期中各年級僅得轉出，不得轉入（特殊理由經入學審查委員會或市府核准者除外）
+• 學生赴國外或大陸地區就學應辦理轉出，無法保留學籍
+• 學期中轉出的缺額，於寒假及暑假辦理補實，志願轉入學生按戶籍遷入時間先後公開分發
+• 中輟生學籍保留原校，得依規定復學
+📌 說明
+• 依 115 作業規定陸</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1252,16 +1320,19 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>📅【115學年度重要時程】
-• 03/06（五）前：透過國小寄發新生入學通知單（黃單）
-• 03/12（四）前：共同學區欲同時登記另一所總量國中者提出申請
-• 03/14（六）08:00–11:00：新生入學現場登記（資格審核）⭐
-• 03/23（一）16:00：公布錄取名冊、候補名冊（註明順位）、未錄取名冊（校網首頁及警衛室）
-• 03/30（一）–04/04（六）：正取生線上報到
-• 04/07（二）–04/08（三）：未線上報到者至警衛室實體報到（擇一即可）
-• 04/15（三）前：缺額候補遞補（電話通知）
-• 04/17（一）前：函送改分發名冊；04/20（一）前改分發國中寄通知
-• 05/30（六）09:00–11:30：新生入學測驗（創意樓，當日發暑假作業）</t>
+          <t>📅 結果：3/23（一）16:00 放榜；3/30 至 4/4 線上報到
+📋 115 學年度重要時程
+• 3/6（五）前：透過國小寄發新生入學通知單（黃單）
+• 3/12（四）前：共同學區欲同時登記另一所總量國中者提出申請
+• 3/14（六）08:00 至 11:00：新生入學現場登記（資格審核）
+• 3/23（一）16:00：公布錄取名冊、候補名冊、未錄取名冊（校網首頁及警衛室）
+• 3/30（一）至 4/4（六）：正取生線上報到
+• 4/7（二）至 4/8（三）：未線上報到者至警衛室實體報到（擇一即可）
+• 4/15（三）前：缺額候補遞補（電話通知）
+• 4/17（一）前：函送改分發名冊；4/20（一）前改分發國中寄通知
+• 5/30（六）09:00 至 11:30：新生入學測驗（創意樓，當日發暑假作業）
+📌 說明
+• 依 115 作業規定柒；說明會「重要日程統整」</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1296,13 +1367,15 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ℹ️【竹光國中 115學年度總量管制基本資訊】
-• 什麼是總量管制：本校入學需求遠超過校舍容量，依市府核定實施「班級總量限制」，新生依順位與設籍時間排序錄取，額滿者改分發他校。
-• 核定招生：115學年度預計招收 12 班
+          <t>ℹ️ 結果：115 學年度預計招收 12 班
+📋 基本資訊
+• 什麼是總量管制：入學需求超過校舍容量，依市府核定實施班級總量限制，新生依順位與設籍時間排序錄取，額滿改分發他校
 • 承辦單位：教務處註冊組
 • 諮詢專線：(03) 524-6683 分機 613
 • 學校地址：新竹市北區和平路 1 號
-• 官方網站：https://www.zgjh.hc.edu.tw</t>
+• 官方網站：https://www.zgjh.hc.edu.tw
+📌 說明
+• 依 115 作業規定貳、參；Q&amp;A 第 4 題</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1337,13 +1410,15 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>🏠【租屋家庭順位速查】
-租屋者只要戶籍符合（學生設籍學區＋直系尊親屬同戶）都可以登記，順位看租約狀態：
-• 有「法院公證」租約 ➔ 第二順位（外縣市國小畢業為第三順位）
-• 只有「未公證」租約 ➔ 第四順位
-• 沒有租約／租約不符規定 ➔ 第五順位
-租約條件：租期涵蓋 115/3/14～115/9/1，承租人須為學生的直系尊親屬或法定監護人。
-再告訴我「有公證」「沒公證」或「沒有租約」，我幫您精確判定！</t>
+          <t>🏠 結果：租屋者可以登記，順位看租約狀態
+📋 三種情況
+• 有「法院公證」租約：第二順位（外縣市國小畢業為第三順位）
+• 只有「未公證」租約：第四順位
+• 沒有租約，或租約不符規定：第五順位
+📌 說明
+• 先決條件：學生設籍學區＋直系尊親屬同戶＋簽家訪同意書
+• 租約條件：租期涵蓋 115/3/14 至 115/9/1，承租人為學生的直系尊親屬或法定監護人
+💡 再告訴我「有公證」「沒公證」或「沒有租約」，我幫您精確判定</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
